--- a/public/downloads/consilegy-security-checklist-2026-10e.xlsx
+++ b/public/downloads/consilegy-security-checklist-2026-10e.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="10" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>事故が起きたときの対応手順（報告、初動、影響の確認、通知、再発防止）を社内規程に定め、机上訓練で確かめています。Revenue CRMの利用規約では、お預かりした個人情報の漏えいなどを当社が知ったときは、遅くとも3営業日以内に契約者へ通知すると定めています。</t>
+          <t>事故が起きたときの対応手順（報告、初動、影響の確認、通知、再発防止）を社内規程に定め、机上訓練で確かめています。Revenue CRMの利用規約では、お預かりした個人情報の漏えいなどを当社が知ったときは、速やかに、遅くとも3営業日以内に契約者へ通知すると定めています。</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>管理ツール</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>業務端末のOS・ソフトウェアは常に最新の状態に更新しています。</t>
+          <t>業務端末はOS・ソフトウェアの自動更新を有効にし、更新が出たら速やかに適用しています。</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>データベースは毎日自動でバックアップを取り、直近7日分を保管しています。添付ファイルも毎日別の保管場所へ複製し、7日分を残しています。バックアップからの復旧テストも行っています。</t>
+          <t>データベースは毎日自動でバックアップを取り、直近7日分を保管しています。添付ファイルも毎日、同じ基盤の中の別の保管領域へ複製し、7日分を残しています。バックアップからの復旧テストも行っています。</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>データベース、ファイル、アプリケーションの実行環境は、いずれも日本（東京リージョン）にあります。AI機能に入力した内容は米国のAI事業者（Anthropic、OpenAI、Google）が、本サービスから送るメールは米国の事業者（Resend）が処理します。AI機能は、契約者が自ら契約するAI事業者に切り替えることもできます。</t>
+          <t>データベース、ファイル、アプリケーションの実行環境は、いずれも日本（東京リージョン）にあります。AI機能で扱うデータ（入力した文章のほか、AI機能が参照するコンタクト・商談・会議の記録などの登録データを含みます）は、米国のAI事業者（Anthropic、OpenAI、Google）が処理します。本サービスから送るメールは、米国の事業者（Resend）が処理します。AI機能は、契約者が自ら契約するAI事業者に切り替えられます。</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>Revenue CRMでは、役割（オーナー・管理者・メンバー）に加え、データの種類ごとに閲覧・作成・編集・削除・書き出しの権限と、見える範囲（全体・チーム・自分）を設定できます。会社ごとのデータはデータベースの行単位のアクセス制御（RLS）で隔離し、この制御を通らないサーバー側の処理も必ず会社で絞り込むことをルールにして、変更のたびに自動の検査で確かめています。</t>
+          <t>Revenue CRMでは、役割（オーナー・管理者・メンバー）ごとに、データの種類別の閲覧・作成・編集・削除・書き出しの権限と、見える範囲（全体・チーム・自分）を設定できます。会社ごとのデータはデータベースの行単位のアクセス制御（RLS）で分けて管理し、RLSを通らないサーバー側の処理についても、会社をまたいでデータを扱う処理がないかを変更のたびに自動で検査しています。</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワード、またはGoogleアカウントでログインできます。多要素認証は、認証アプリのワンタイムコードとバックアップコードで設定でき、端末をなくしたときは同じ会社の管理者が解除できます。SAMLによるシングルサインオンには対応していません。</t>
+          <t>メールアドレスとパスワード、またはGoogleアカウントでログインできます。多要素認証は、認証アプリのワンタイムコードとバックアップコードで設定でき、端末をなくしたときは同じ会社の管理者が解除できます。SAMLによるシングルサインオンには対応していません。管理者が多要素認証を解除した記録は監査ログに残ります。多要素認証を会社として全員に必須にする設定は、現時点ではありません。</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="D29" s="20" t="n"/>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>データベース・ファイルの保管：Supabase（日本・東京）／アプリケーションの実行：Vercel（日本・東京）／AI機能：Anthropic、OpenAI、Google（米国）／メール送信：Resend（米国）／決済：Stripe（米国）、PayPal（シンガポール）／ログイン時の自動化対策：Cloudflare（米国）／不正利用を防ぐためのアクセス回数の制限：Upstash（日本・東京）。詳細は利用規約の外部委託先一覧をご覧ください。</t>
+          <t>データベース・ファイルの保管：Supabase（日本・東京）／アプリケーションの実行：Vercel（日本・東京）／AI機能：Anthropic、OpenAI、Google（米国）／メール送信：Resend（米国）／決済：Stripe（米国）、PayPal（シンガポール）／ログイン時の自動化対策：Cloudflare（米国）／不正利用を防ぐためのアクセス回数の制限：Upstash（日本・東京）。決済、ログイン時の自動化対策、回数制限の事業者は、Revenue CRMに登録されたデータを受け取りません。詳細は利用規約の外部委託先一覧をご覧ください。</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>入力されたデータを、AIモデルの学習に使うことも、使わせることもありません。利用規約で、登録データを外部のAI事業者のモデル学習に使わせないことを定めています。AI機能は各社のAPIを通じて利用しており、APIの利用条件上、送信した内容はモデルの学習に使われません。なお、各事業者は不正利用の監視のため、送信された内容を一定期間保持することがあります。</t>
+          <t>入力されたデータを、AIモデルの学習に使うことも、使わせることもありません。利用規約で、当社が利用する外部のAI事業者に登録データをモデルの学習に使わせないことを定めており、各社のAPIを学習に使われない条件で利用しています。契約者が自ら契約したAI事業者に切り替えた場合は、その事業者の利用条件によります。なお、各事業者は不正利用の監視のため、送信された内容を一定期間保持することがあります。</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>第三者による脆弱性診断やペネトレーションテストは、現時点では受けていません。開発では変更のたびに、ほかの会社のデータを参照する処理がないか、RLSの設定漏れがないかを自動で検査しています。システムで使っている外部のソフトウェアに脆弱性が見つかると自動で通知が届くようにしており、通知が届くたびに更新しています。</t>
+          <t>第三者による脆弱性診断やペネトレーションテストは、現時点では受けていません。開発では変更のたびに、ほかの会社のデータを扱う処理がないか、RLSの設定漏れがないかを自動で検査しています。システムで使っている外部のソフトウェアの更新や脆弱性の情報が自動で届くようにしており、内容を確かめたうえで、深刻度に応じて更新しています。</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,32 @@
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>お客様のデータや検索結果をAIに渡すときは、AIへの指示と混ざらないように分けて渡しています。AIに不正な指示を与えようとする文が紛れていないかも確かめ、見つけたものは記録しています。AIが作成した内容には「AI生成」と表示します。AIとのやり取りは記録に残し、その記録は90日たつと自動で削除します。</t>
+          <t>AIに渡すお客様のデータや検索結果は、原則としてAIへの指示と分けて渡しています。データの中にAIへの不正な指示らしい文がないかも確かめ、見つけたものはサーバーのログに残しています。AIが作成した内容には、主な画面で「AI生成」と表示します。AIとのやり取りは記録に残し、その記録は90日たつと自動で削除します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>外国にある事業者に個人データの取扱いを委託していますか</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>AI機能とメール送信で、米国の事業者に取扱いを委託しています。委託先とは、契約で、目的外の利用の禁止（モデルの学習に使わせないことを含みます）、暗号化とアクセス制御、再委託先への同じ義務、漏えい時の通知、処理後の削除を確かめています。委託先と所在国は、Revenue CRM利用規約の外部委託先一覧に載せています。</t>
         </is>
       </c>
     </row>
